--- a/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/Evaluations 2/Digital Chess Clock/Grading/2 stage/2026-03-16/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Digital Chess Clock/Grading/2 stage/6-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0F34AB-20C3-A745-84B8-704B714A4C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BF2897-C2BF-F44D-AC5B-2A6B05E14882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16180" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chess Clock" sheetId="1" r:id="rId1"/>
@@ -1066,6 +1066,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1078,7 +1079,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15621,16 +15621,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
       <c r="J1" s="23" t="s">
         <v>111</v>
       </c>
@@ -15944,16 +15944,16 @@
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="24" t="s">
@@ -15986,7 +15986,7 @@
         <v>123</v>
       </c>
       <c r="B14" s="27">
-        <f>COUNTIF('Chess Clock'!$A$2:$A$44, A14)</f>
+        <f>COUNTIF('Chess Clock'!$A$2:$A$46, A14)</f>
         <v>3</v>
       </c>
       <c r="C14" s="28">
@@ -16019,8 +16019,8 @@
         <v>2</v>
       </c>
       <c r="B15" s="27">
-        <f>COUNTIF('Chess Clock'!$A$2:$A$44, A15)</f>
-        <v>12</v>
+        <f>COUNTIF('Chess Clock'!$A$2:$A$46, A15)</f>
+        <v>13</v>
       </c>
       <c r="C15" s="28">
         <f>SUMIF('LLM Grading'!$A$2:$A$46, $A15, 'LLM Grading'!$C$2:$C$46)</f>
@@ -16040,11 +16040,11 @@
       </c>
       <c r="G15" s="28">
         <f t="shared" si="6"/>
-        <v>0.66666666666666663</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="H15" s="28">
         <f t="shared" si="7"/>
-        <v>0.72727272727272718</v>
+        <v>0.69565217391304346</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -16052,8 +16052,8 @@
         <v>4</v>
       </c>
       <c r="B16" s="27">
-        <f>COUNTIF('Chess Clock'!$A$2:$A$44, A16)</f>
-        <v>13</v>
+        <f>COUNTIF('Chess Clock'!$A$2:$A$46, A16)</f>
+        <v>14</v>
       </c>
       <c r="C16" s="28">
         <f>SUMIF('LLM Grading'!$A$2:$A$46, $A16, 'LLM Grading'!$C$2:$C$46)</f>
@@ -16073,11 +16073,11 @@
       </c>
       <c r="G16" s="28">
         <f t="shared" si="6"/>
-        <v>0.61538461538461542</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H16" s="28">
         <f t="shared" si="7"/>
-        <v>0.76190476190476197</v>
+        <v>0.72727272727272729</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -16151,7 +16151,7 @@
         <v>31</v>
       </c>
       <c r="B19" s="27">
-        <f>COUNTIF('Chess Clock'!$A$2:$A$44, A19)</f>
+        <f>COUNTIF('Chess Clock'!$A$2:$A$46, A19)</f>
         <v>1</v>
       </c>
       <c r="C19" s="28">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="B21" s="28">
         <f t="shared" ref="B21:E21" si="8">SUM(B14:B20)</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" s="28">
         <f t="shared" si="8"/>
@@ -16238,11 +16238,11 @@
       </c>
       <c r="G21" s="28">
         <f t="shared" si="6"/>
-        <v>0.68604651162790697</v>
+        <v>0.65555555555555556</v>
       </c>
       <c r="H21" s="28">
         <f t="shared" si="7"/>
-        <v>0.7814569536423841</v>
+        <v>0.76129032258064522</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17266,24 +17266,24 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="70" t="s">
+      <c r="C1" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="70" t="s">
+      <c r="D1" s="64" t="s">
         <v>62</v>
       </c>
       <c r="E1" s="30"/>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="L1" s="68" t="s">
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="L1" s="69" t="s">
         <v>125</v>
       </c>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="str">
@@ -17553,17 +17553,17 @@
         <v>0.5</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="L8" s="68" t="s">
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="L8" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -17830,17 +17830,17 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="30"/>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="67" t="s">
         <v>142</v>
       </c>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
-      <c r="L15" s="68" t="s">
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="L15" s="69" t="s">
         <v>143</v>
       </c>
-      <c r="M15" s="69"/>
-      <c r="N15" s="69"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -18107,17 +18107,17 @@
         <v>0</v>
       </c>
       <c r="E22" s="30"/>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="L22" s="68" t="s">
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="L22" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -18384,17 +18384,17 @@
         <v>1</v>
       </c>
       <c r="E29" s="30"/>
-      <c r="F29" s="66" t="s">
+      <c r="F29" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="67"/>
-      <c r="L29" s="68" t="s">
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="L29" s="69" t="s">
         <v>147</v>
       </c>
-      <c r="M29" s="69"/>
-      <c r="N29" s="69"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="70"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -18661,17 +18661,17 @@
         <v>0</v>
       </c>
       <c r="E36" s="30"/>
-      <c r="F36" s="66" t="s">
+      <c r="F36" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
-      <c r="L36" s="68" t="s">
+      <c r="G36" s="68"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="68"/>
+      <c r="L36" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="M36" s="69"/>
-      <c r="N36" s="69"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
     </row>
     <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -18938,17 +18938,17 @@
         <v>1</v>
       </c>
       <c r="E43" s="30"/>
-      <c r="F43" s="66" t="s">
+      <c r="F43" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="G43" s="67"/>
-      <c r="H43" s="67"/>
-      <c r="I43" s="67"/>
-      <c r="L43" s="68" t="s">
+      <c r="G43" s="68"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="68"/>
+      <c r="L43" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="M43" s="69"/>
-      <c r="N43" s="69"/>
+      <c r="M43" s="70"/>
+      <c r="N43" s="70"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -19215,17 +19215,17 @@
         <v>1</v>
       </c>
       <c r="E50" s="30"/>
-      <c r="F50" s="66" t="s">
+      <c r="F50" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="G50" s="67"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="67"/>
-      <c r="L50" s="68" t="s">
+      <c r="G50" s="68"/>
+      <c r="H50" s="68"/>
+      <c r="I50" s="68"/>
+      <c r="L50" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="M50" s="69"/>
-      <c r="N50" s="69"/>
+      <c r="M50" s="70"/>
+      <c r="N50" s="70"/>
     </row>
     <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -20534,25 +20534,25 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="70" t="s">
+      <c r="C1" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="70" t="s">
+      <c r="D1" s="64" t="s">
         <v>62</v>
       </c>
       <c r="E1" s="30"/>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="L1" s="66" t="s">
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="L1" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
     </row>
     <row r="2" spans="1:24" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="str">
@@ -20956,12 +20956,12 @@
         <v>1</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -21351,12 +21351,12 @@
         <v>0</v>
       </c>
       <c r="E15" s="30"/>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="67" t="s">
         <v>142</v>
       </c>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -21746,12 +21746,12 @@
         <v>1</v>
       </c>
       <c r="E22" s="30"/>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
     </row>
     <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -22141,12 +22141,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="30"/>
-      <c r="F29" s="66" t="s">
+      <c r="F29" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="67"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -22536,12 +22536,12 @@
         <v>1</v>
       </c>
       <c r="E36" s="30"/>
-      <c r="F36" s="66" t="s">
+      <c r="F36" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="68"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -22931,12 +22931,12 @@
         <v>1</v>
       </c>
       <c r="E43" s="30"/>
-      <c r="F43" s="66" t="s">
+      <c r="F43" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="G43" s="67"/>
-      <c r="H43" s="67"/>
-      <c r="I43" s="67"/>
+      <c r="G43" s="68"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="68"/>
     </row>
     <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -23326,12 +23326,12 @@
         <v>0</v>
       </c>
       <c r="E50" s="30"/>
-      <c r="F50" s="66" t="s">
+      <c r="F50" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="G50" s="67"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="67"/>
+      <c r="G50" s="68"/>
+      <c r="H50" s="68"/>
+      <c r="I50" s="68"/>
     </row>
     <row r="51" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">

--- a/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Digital Chess Clock/Grading/2 stage/6-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BF2897-C2BF-F44D-AC5B-2A6B05E14882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C59962-3FBE-6E42-8173-BE4C9F5F8FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16180" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16180" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chess Clock" sheetId="1" r:id="rId1"/>
@@ -644,7 +644,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -901,11 +901,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1071,14 +1080,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1371,7 +1383,9 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Element"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Human"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LLM"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LLM">
+      <calculatedColumnFormula>'LLM Grading'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Weighted Cohens Kappa-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17273,17 +17287,17 @@
         <v>62</v>
       </c>
       <c r="E1" s="30"/>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="69" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="L1" s="69" t="s">
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="L1" s="67" t="s">
         <v>125</v>
       </c>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="str">
@@ -17553,17 +17567,17 @@
         <v>0.5</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="67" t="s">
+      <c r="F8" s="69" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="L8" s="69" t="s">
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="L8" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -17830,17 +17844,17 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="30"/>
-      <c r="F15" s="67" t="s">
+      <c r="F15" s="69" t="s">
         <v>142</v>
       </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="L15" s="69" t="s">
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="L15" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -18107,17 +18121,17 @@
         <v>0</v>
       </c>
       <c r="E22" s="30"/>
-      <c r="F22" s="67" t="s">
+      <c r="F22" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="L22" s="69" t="s">
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="L22" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -18384,17 +18398,17 @@
         <v>1</v>
       </c>
       <c r="E29" s="30"/>
-      <c r="F29" s="67" t="s">
+      <c r="F29" s="69" t="s">
         <v>146</v>
       </c>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
-      <c r="L29" s="69" t="s">
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="L29" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -18661,17 +18675,17 @@
         <v>0</v>
       </c>
       <c r="E36" s="30"/>
-      <c r="F36" s="67" t="s">
+      <c r="F36" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
-      <c r="L36" s="69" t="s">
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="L36" s="67" t="s">
         <v>149</v>
       </c>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70"/>
+      <c r="M36" s="68"/>
+      <c r="N36" s="68"/>
     </row>
     <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -18938,17 +18952,17 @@
         <v>1</v>
       </c>
       <c r="E43" s="30"/>
-      <c r="F43" s="67" t="s">
+      <c r="F43" s="69" t="s">
         <v>150</v>
       </c>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
-      <c r="L43" s="69" t="s">
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="L43" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="M43" s="70"/>
-      <c r="N43" s="70"/>
+      <c r="M43" s="68"/>
+      <c r="N43" s="68"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -19215,17 +19229,17 @@
         <v>1</v>
       </c>
       <c r="E50" s="30"/>
-      <c r="F50" s="67" t="s">
+      <c r="F50" s="69" t="s">
         <v>152</v>
       </c>
-      <c r="G50" s="68"/>
-      <c r="H50" s="68"/>
-      <c r="I50" s="68"/>
-      <c r="L50" s="69" t="s">
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="L50" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="M50" s="70"/>
-      <c r="N50" s="70"/>
+      <c r="M50" s="68"/>
+      <c r="N50" s="68"/>
     </row>
     <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -20477,6 +20491,12 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="L15:N15"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="L50:N50"/>
@@ -20487,12 +20507,6 @@
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="F43:I43"/>
     <mergeCell ref="L43:N43"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="L15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -20541,18 +20555,18 @@
         <v>62</v>
       </c>
       <c r="E1" s="30"/>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="69" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="L1" s="67" t="s">
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="L1" s="69" t="s">
         <v>154</v>
       </c>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
     </row>
     <row r="2" spans="1:24" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="str">
@@ -20568,7 +20582,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="4">
-        <f>'Human Grading'!C2</f>
+        <f>'LLM Grading'!C2</f>
         <v>1</v>
       </c>
       <c r="E2" s="30"/>
@@ -20638,7 +20652,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <f>'Human Grading'!C3</f>
+        <f>'LLM Grading'!C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="30"/>
@@ -20647,19 +20661,19 @@
       </c>
       <c r="G3" s="38">
         <f>COUNTIFS($C$2:$C$90, $F3, $D$2:$D$90, G$2)</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H3" s="39">
         <f>COUNTIFS($C$2:$C$46, $F3, $D$2:$D$46, H$2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="40">
         <f>COUNTIFS($C$2:$C$46, $F3, $D$2:$D$46, I$2)+MAX(D47-C47,0)+MAX(D48-C48,0)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)+MAX(D53-C53,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" ref="J3:J5" si="0">SUM(G3:I3)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" s="11"/>
       <c r="L3" s="37">
@@ -20683,15 +20697,15 @@
       </c>
       <c r="R3" s="38">
         <f t="shared" ref="R3:T3" si="2">($J3/$J$6) * (G$6/$J$6)</f>
-        <v>4.4748520710059171E-2</v>
+        <v>7.6895692417230335E-2</v>
       </c>
       <c r="S3" s="39">
         <f t="shared" si="2"/>
-        <v>4.0680473372781065E-3</v>
+        <v>2.135991456034176E-2</v>
       </c>
       <c r="T3" s="40">
         <f t="shared" si="2"/>
-        <v>0.16272189349112426</v>
+        <v>0.12815948736205054</v>
       </c>
       <c r="U3" s="11"/>
       <c r="V3" s="41" t="s">
@@ -20699,7 +20713,7 @@
       </c>
       <c r="W3" s="38">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
-        <v>0</v>
+        <v>0.32075471698113206</v>
       </c>
       <c r="X3" s="40" t="s">
         <v>156</v>
@@ -20719,7 +20733,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <f>'Human Grading'!C4</f>
+        <f>'LLM Grading'!C4</f>
         <v>1</v>
       </c>
       <c r="E4" s="30"/>
@@ -20764,15 +20778,15 @@
       </c>
       <c r="R4" s="42">
         <f t="shared" ref="R4:T4" si="5">($J4/$J$6) * (G$6/$J$6)</f>
-        <v>4.0680473372781065E-3</v>
+        <v>6.4079743681025271E-3</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" si="5"/>
-        <v>3.6982248520710064E-4</v>
+        <v>1.77999288002848E-3</v>
       </c>
       <c r="T4" s="43">
         <f t="shared" si="5"/>
-        <v>1.4792899408284025E-2</v>
+        <v>1.0679957280170878E-2</v>
       </c>
       <c r="U4" s="11"/>
       <c r="V4" s="41" t="s">
@@ -20780,7 +20794,7 @@
       </c>
       <c r="W4" s="42">
         <f>SUMPRODUCT(R3:T5, M3:O5)</f>
-        <v>0.34430473372781067</v>
+        <v>0.43930224279102881</v>
       </c>
       <c r="X4" s="43" t="s">
         <v>158</v>
@@ -20800,7 +20814,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <f>'Human Grading'!C5</f>
+        <f>'LLM Grading'!C5</f>
         <v>1</v>
       </c>
       <c r="E5" s="30"/>
@@ -20809,15 +20823,15 @@
       </c>
       <c r="G5" s="44">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, G$2)+MAX(C47-D47,0)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)+MAX(C52-D52,0)+MAX(C53-D53,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H5" s="45">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, H$2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="46">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, I$2)+ SUM(MIN(C47,D47), MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51), MIN(C52,D52), MIN(C53,D53))</f>
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J5" s="11">
         <f t="shared" si="0"/>
@@ -20845,15 +20859,15 @@
       </c>
       <c r="R5" s="44">
         <f t="shared" ref="R5:T5" si="7">($J5/$J$6) * (G$6/$J$6)</f>
-        <v>0.16272189349112426</v>
+        <v>0.25631897472410109</v>
       </c>
       <c r="S5" s="45">
         <f t="shared" si="7"/>
-        <v>1.4792899408284025E-2</v>
+        <v>7.1199715201139199E-2</v>
       </c>
       <c r="T5" s="46">
         <f t="shared" si="7"/>
-        <v>0.59171597633136097</v>
+        <v>0.42719829120683517</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="41" t="s">
@@ -20861,7 +20875,7 @@
       </c>
       <c r="W5" s="44">
         <f>1-W3/W4</f>
-        <v>1</v>
+        <v>0.26985413290113447</v>
       </c>
       <c r="X5" s="46" t="s">
         <v>159</v>
@@ -20881,7 +20895,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <f>'Human Grading'!C6</f>
+        <f>'LLM Grading'!C6</f>
         <v>1</v>
       </c>
       <c r="E6" s="30"/>
@@ -20890,19 +20904,19 @@
       </c>
       <c r="G6" s="11">
         <f t="shared" ref="G6:I6" si="8">SUM(G3:G5)</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="8"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J6" s="11">
         <f>SUM(G3:I5)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
@@ -20930,7 +20944,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="4">
-        <f>'Human Grading'!C7</f>
+        <f>'LLM Grading'!C7</f>
         <v>1</v>
       </c>
       <c r="E7" s="30"/>
@@ -20952,16 +20966,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <f>'Human Grading'!C8</f>
-        <v>1</v>
+        <f>'LLM Grading'!C8</f>
+        <v>0.5</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="67" t="s">
+      <c r="F8" s="69" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -20977,8 +20991,8 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <f>'Human Grading'!C9</f>
-        <v>1</v>
+        <f>'LLM Grading'!C9</f>
+        <v>0</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="11" t="s">
@@ -21047,8 +21061,8 @@
         <v>1</v>
       </c>
       <c r="D10" s="4">
-        <f>'Human Grading'!C10</f>
-        <v>1</v>
+        <f>'LLM Grading'!C10</f>
+        <v>0</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="37">
@@ -21056,19 +21070,19 @@
       </c>
       <c r="G10" s="38">
         <f t="shared" ref="G10:H10" si="9">COUNTIFS($A$2:$A$90,$F$9,$C$2:$C$90,$F10,$D$2:$D$90,G$9)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="39">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="40">
         <f>COUNTIFS($A$2:$A$46,$F$9,$C$2:$C$46,$F10,$D$2:$D$46,I$9)+MAX(D47-C47,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="11">
         <f t="shared" ref="J10:J12" si="10">SUM(G10:I10)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="37">
@@ -21092,15 +21106,15 @@
       </c>
       <c r="R10" s="38">
         <f t="shared" ref="R10:T10" si="12">($J10/$J$13) * (G$13/$J$13)</f>
-        <v>2.0408163265306121E-2</v>
+        <v>7.1005917159763315E-2</v>
       </c>
       <c r="S10" s="39">
         <f t="shared" si="12"/>
-        <v>1.020408163265306E-2</v>
+        <v>3.5502958579881658E-2</v>
       </c>
       <c r="T10" s="40">
         <f t="shared" si="12"/>
-        <v>0.11224489795918366</v>
+        <v>0.1242603550295858</v>
       </c>
       <c r="U10" s="11"/>
       <c r="V10" s="41" t="s">
@@ -21108,7 +21122,7 @@
       </c>
       <c r="W10" s="38">
         <f>SUMPRODUCT(G10:I12, M10:O12) /$J$13</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X10" s="40" t="s">
         <v>156</v>
@@ -21128,7 +21142,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="4">
-        <f>'Human Grading'!C11</f>
+        <f>'LLM Grading'!C11</f>
         <v>1</v>
       </c>
       <c r="E11" s="30"/>
@@ -21173,15 +21187,15 @@
       </c>
       <c r="R11" s="42">
         <f t="shared" ref="R11:T11" si="15">($J11/$J$13) * (G$13/$J$13)</f>
-        <v>1.020408163265306E-2</v>
+        <v>2.3668639053254441E-2</v>
       </c>
       <c r="S11" s="11">
         <f t="shared" si="15"/>
-        <v>5.1020408163265302E-3</v>
+        <v>1.183431952662722E-2</v>
       </c>
       <c r="T11" s="43">
         <f t="shared" si="15"/>
-        <v>5.612244897959183E-2</v>
+        <v>4.142011834319527E-2</v>
       </c>
       <c r="U11" s="11"/>
       <c r="V11" s="41" t="s">
@@ -21189,7 +21203,7 @@
       </c>
       <c r="W11" s="42">
         <f>SUMPRODUCT(R10:T12, M10:O12)</f>
-        <v>0.29081632653061223</v>
+        <v>0.44082840236686388</v>
       </c>
       <c r="X11" s="43" t="s">
         <v>158</v>
@@ -21209,7 +21223,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="4">
-        <f>'Human Grading'!C12</f>
+        <f>'LLM Grading'!C12</f>
         <v>1</v>
       </c>
       <c r="E12" s="30"/>
@@ -21218,7 +21232,7 @@
       </c>
       <c r="G12" s="44">
         <f>COUNTIFS($A$2:$A$46,$F$9,$C$2:$C$46,$F12,$D$2:$D$46,G$9)+MAX(C47-D47,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" s="45">
         <f>COUNTIFS($A$2:$A$90,$F$9,$C$2:$C$90,$F12,$D$2:$D$90,H$9)</f>
@@ -21226,11 +21240,11 @@
       </c>
       <c r="I12" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$9,$C$2:$C$46,$F12,$D$2:$D$46,I$9)+MIN(C47-D47)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J12" s="11">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="37">
@@ -21254,15 +21268,15 @@
       </c>
       <c r="R12" s="44">
         <f t="shared" ref="R12:T12" si="17">($J12/$J$13) * (G$13/$J$13)</f>
-        <v>0.11224489795918366</v>
+        <v>0.21301775147928995</v>
       </c>
       <c r="S12" s="45">
         <f t="shared" si="17"/>
-        <v>5.612244897959183E-2</v>
+        <v>0.10650887573964497</v>
       </c>
       <c r="T12" s="46">
         <f t="shared" si="17"/>
-        <v>0.61734693877551017</v>
+        <v>0.37278106508875736</v>
       </c>
       <c r="U12" s="11"/>
       <c r="V12" s="41" t="s">
@@ -21270,7 +21284,7 @@
       </c>
       <c r="W12" s="44">
         <f>1-W10/W11</f>
-        <v>1</v>
+        <v>-0.13422818791946312</v>
       </c>
       <c r="X12" s="46" t="s">
         <v>159</v>
@@ -21290,7 +21304,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="4">
-        <f>'Human Grading'!C13</f>
+        <f>'LLM Grading'!C13</f>
         <v>1</v>
       </c>
       <c r="E13" s="30"/>
@@ -21299,19 +21313,19 @@
       </c>
       <c r="G13" s="11">
         <f t="shared" ref="G13:I13" si="18">SUM(G10:G12)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="11">
         <f t="shared" si="18"/>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J13" s="11">
         <f>SUM(G10:I12)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21328,7 +21342,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="4">
-        <f>'Human Grading'!C14</f>
+        <f>'LLM Grading'!C14</f>
         <v>1</v>
       </c>
       <c r="E14" s="30"/>
@@ -21347,16 +21361,16 @@
         <v>0</v>
       </c>
       <c r="D15" s="4">
-        <f>'Human Grading'!C15</f>
-        <v>0</v>
+        <f>'LLM Grading'!C15</f>
+        <v>0.5</v>
       </c>
       <c r="E15" s="30"/>
-      <c r="F15" s="67" t="s">
+      <c r="F15" s="69" t="s">
         <v>142</v>
       </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -21372,7 +21386,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="4">
-        <f>'Human Grading'!C16</f>
+        <f>'LLM Grading'!C16</f>
         <v>0</v>
       </c>
       <c r="E16" s="30"/>
@@ -21442,8 +21456,8 @@
         <v>1</v>
       </c>
       <c r="D17" s="4">
-        <f>'Human Grading'!C17</f>
-        <v>1</v>
+        <f>'LLM Grading'!C17</f>
+        <v>0</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="37">
@@ -21451,11 +21465,11 @@
       </c>
       <c r="G17" s="38">
         <f t="shared" ref="G17:H17" si="19">COUNTIFS($A$2:$A$90,$F$16,$C$2:$C$90,$F17,$D$2:$D$90,G$16)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" s="39">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" s="40">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F17,$D$2:$D$46,I$16) + MAX(D48-C48,0)</f>
@@ -21487,15 +21501,15 @@
       </c>
       <c r="R17" s="38">
         <f t="shared" ref="R17:T17" si="22">($J17/$J$20) * (G$20/$J$20)</f>
-        <v>4.0000000000000008E-2</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="S17" s="39">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>2.6666666666666668E-2</v>
       </c>
       <c r="T17" s="40">
         <f t="shared" si="22"/>
-        <v>0.16000000000000003</v>
+        <v>9.3333333333333338E-2</v>
       </c>
       <c r="U17" s="11"/>
       <c r="V17" s="41" t="s">
@@ -21503,7 +21517,7 @@
       </c>
       <c r="W17" s="38">
         <f>SUMPRODUCT(G17:I19, M17:O19) /$J$20</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X17" s="40" t="s">
         <v>156</v>
@@ -21523,8 +21537,8 @@
         <v>1</v>
       </c>
       <c r="D18" s="4">
-        <f>'Human Grading'!C18</f>
-        <v>1</v>
+        <f>'LLM Grading'!C18</f>
+        <v>0</v>
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="37">
@@ -21584,7 +21598,7 @@
       </c>
       <c r="W18" s="42">
         <f>SUMPRODUCT(R17:T19, M17:O19)</f>
-        <v>0.32000000000000006</v>
+        <v>0.48000000000000009</v>
       </c>
       <c r="X18" s="43" t="s">
         <v>158</v>
@@ -21604,8 +21618,8 @@
         <v>1</v>
       </c>
       <c r="D19" s="4">
-        <f>'Human Grading'!C19</f>
-        <v>1</v>
+        <f>'LLM Grading'!C19</f>
+        <v>0</v>
       </c>
       <c r="E19" s="30"/>
       <c r="F19" s="37">
@@ -21613,7 +21627,7 @@
       </c>
       <c r="G19" s="44">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F19,$D$2:$D$46,G$16)+MAX(C48-D48,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H19" s="45">
         <f>COUNTIFS($A$2:$A$90,$F$16,$C$2:$C$90,$F19,$D$2:$D$90,H$16)</f>
@@ -21621,7 +21635,7 @@
       </c>
       <c r="I19" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F19,$D$2:$D$46,I$16) + MIN(C48,D48)</f>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J19" s="11">
         <f t="shared" si="20"/>
@@ -21649,15 +21663,15 @@
       </c>
       <c r="R19" s="44">
         <f t="shared" ref="R19:T19" si="27">($J19/$J$20) * (G$20/$J$20)</f>
-        <v>0.16000000000000003</v>
+        <v>0.32000000000000006</v>
       </c>
       <c r="S19" s="45">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>0.10666666666666667</v>
       </c>
       <c r="T19" s="46">
         <f t="shared" si="27"/>
-        <v>0.64000000000000012</v>
+        <v>0.37333333333333335</v>
       </c>
       <c r="U19" s="11"/>
       <c r="V19" s="41" t="s">
@@ -21665,7 +21679,7 @@
       </c>
       <c r="W19" s="44">
         <f>1-W17/W18</f>
-        <v>1</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="X19" s="46" t="s">
         <v>159</v>
@@ -21685,8 +21699,8 @@
         <v>1</v>
       </c>
       <c r="D20" s="4">
-        <f>'Human Grading'!C20</f>
-        <v>1</v>
+        <f>'LLM Grading'!C20</f>
+        <v>0</v>
       </c>
       <c r="E20" s="30"/>
       <c r="F20" s="47" t="s">
@@ -21694,15 +21708,15 @@
       </c>
       <c r="G20" s="11">
         <f t="shared" ref="G20:I20" si="28">SUM(G17:G19)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="11">
         <f t="shared" si="28"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J20" s="11">
         <f>SUM(G17:I19)</f>
@@ -21723,8 +21737,8 @@
         <v>1</v>
       </c>
       <c r="D21" s="4">
-        <f>'Human Grading'!C21</f>
-        <v>1</v>
+        <f>'LLM Grading'!C21</f>
+        <v>0</v>
       </c>
       <c r="E21" s="30"/>
     </row>
@@ -21742,16 +21756,16 @@
         <v>1</v>
       </c>
       <c r="D22" s="4">
-        <f>'Human Grading'!C22</f>
-        <v>1</v>
+        <f>'LLM Grading'!C22</f>
+        <v>0</v>
       </c>
       <c r="E22" s="30"/>
-      <c r="F22" s="67" t="s">
+      <c r="F22" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
     </row>
     <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -21767,8 +21781,8 @@
         <v>0</v>
       </c>
       <c r="D23" s="4">
-        <f>'Human Grading'!C23</f>
-        <v>0</v>
+        <f>'LLM Grading'!C23</f>
+        <v>0.5</v>
       </c>
       <c r="E23" s="30"/>
       <c r="F23" s="11" t="s">
@@ -21837,7 +21851,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="4">
-        <f>'Human Grading'!C24</f>
+        <f>'LLM Grading'!C24</f>
         <v>1</v>
       </c>
       <c r="E24" s="30"/>
@@ -21886,11 +21900,11 @@
       </c>
       <c r="S24" s="39">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
       <c r="T24" s="40">
         <f t="shared" si="32"/>
-        <v>0.1875</v>
+        <v>0.125</v>
       </c>
       <c r="U24" s="11"/>
       <c r="V24" s="41" t="s">
@@ -21898,7 +21912,7 @@
       </c>
       <c r="W24" s="38">
         <f>SUMPRODUCT(G24:I26, M24:O26) /$J$27</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="X24" s="40" t="s">
         <v>156</v>
@@ -21918,7 +21932,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="4">
-        <f>'Human Grading'!C25</f>
+        <f>'LLM Grading'!C25</f>
         <v>1</v>
       </c>
       <c r="E25" s="30"/>
@@ -21979,7 +21993,7 @@
       </c>
       <c r="W25" s="42">
         <f>SUMPRODUCT(R24:T26, M24:O26)</f>
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="X25" s="43" t="s">
         <v>158</v>
@@ -21999,7 +22013,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="4">
-        <f>'Human Grading'!C26</f>
+        <f>'LLM Grading'!C26</f>
         <v>1</v>
       </c>
       <c r="E26" s="30"/>
@@ -22012,11 +22026,11 @@
       </c>
       <c r="H26" s="45">
         <f>COUNTIFS($A$2:$A$90,$F$23,$C$2:$C$90,$F26,$D$2:$D$90,H$23)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$23,$C$2:$C$46,$F26,$D$2:$D$46,I$23) + MIN(C51,D51)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" s="11">
         <f t="shared" si="30"/>
@@ -22048,11 +22062,11 @@
       </c>
       <c r="S26" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="T26" s="46">
         <f t="shared" si="37"/>
-        <v>0.5625</v>
+        <v>0.375</v>
       </c>
       <c r="U26" s="11"/>
       <c r="V26" s="41" t="s">
@@ -22060,7 +22074,7 @@
       </c>
       <c r="W26" s="44">
         <f>1-W24/W25</f>
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="X26" s="46" t="s">
         <v>159</v>
@@ -22080,7 +22094,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="4">
-        <f>'Human Grading'!C27</f>
+        <f>'LLM Grading'!C27</f>
         <v>1</v>
       </c>
       <c r="E27" s="30"/>
@@ -22093,11 +22107,11 @@
       </c>
       <c r="H27" s="11">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="11">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(G24:I26)</f>
@@ -22118,7 +22132,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="4">
-        <f>'Human Grading'!C28</f>
+        <f>'LLM Grading'!C28</f>
         <v>1</v>
       </c>
       <c r="E28" s="30"/>
@@ -22137,16 +22151,16 @@
         <v>1</v>
       </c>
       <c r="D29" s="4">
-        <f>'Human Grading'!C29</f>
+        <f>'LLM Grading'!C29</f>
         <v>1</v>
       </c>
       <c r="E29" s="30"/>
-      <c r="F29" s="67" t="s">
+      <c r="F29" s="69" t="s">
         <v>146</v>
       </c>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -22162,8 +22176,8 @@
         <v>1</v>
       </c>
       <c r="D30" s="4">
-        <f>'Human Grading'!C30</f>
-        <v>1</v>
+        <f>'LLM Grading'!C30</f>
+        <v>0</v>
       </c>
       <c r="E30" s="30"/>
       <c r="F30" s="11" t="s">
@@ -22232,7 +22246,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="4">
-        <f>'Human Grading'!C31</f>
+        <f>'LLM Grading'!C31</f>
         <v>1</v>
       </c>
       <c r="E31" s="30"/>
@@ -22277,7 +22291,7 @@
       </c>
       <c r="R31" s="38">
         <f t="shared" ref="R31:T31" si="42">($J31/$J$34) * (G$34/$J$34)</f>
-        <v>4.0000000000000008E-2</v>
+        <v>0.12</v>
       </c>
       <c r="S31" s="39">
         <f t="shared" si="42"/>
@@ -22285,7 +22299,7 @@
       </c>
       <c r="T31" s="40">
         <f t="shared" si="42"/>
-        <v>0.16000000000000003</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="U31" s="11"/>
       <c r="V31" s="41" t="s">
@@ -22293,7 +22307,7 @@
       </c>
       <c r="W31" s="38">
         <f>SUMPRODUCT(G31:I33, M31:O33) /$J$34</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X31" s="40" t="s">
         <v>156</v>
@@ -22313,8 +22327,8 @@
         <v>1</v>
       </c>
       <c r="D32" s="4">
-        <f>'Human Grading'!C32</f>
-        <v>1</v>
+        <f>'LLM Grading'!C32</f>
+        <v>0</v>
       </c>
       <c r="E32" s="30"/>
       <c r="F32" s="37">
@@ -22374,7 +22388,7 @@
       </c>
       <c r="W32" s="42">
         <f>SUMPRODUCT(R31:T33, M31:O33)</f>
-        <v>0.32000000000000006</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="X32" s="43" t="s">
         <v>158</v>
@@ -22394,7 +22408,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="4">
-        <f>'Human Grading'!C33</f>
+        <f>'LLM Grading'!C33</f>
         <v>1</v>
       </c>
       <c r="E33" s="30"/>
@@ -22403,7 +22417,7 @@
       </c>
       <c r="G33" s="44">
         <f>COUNTIFS($A$2:$A$46,$F$30,$C$2:$C$46,$F33,$D$2:$D$46,G$30) + MAX(C49-D49,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="45">
         <f>COUNTIFS($A$2:$A$90,$F$30,$C$2:$C$90,$F33,$D$2:$D$90,H$30)</f>
@@ -22411,7 +22425,7 @@
       </c>
       <c r="I33" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$30,$C$2:$C$46,$F33,$D$2:$D$46,I$30) + MIN(C49,D49)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J33" s="11">
         <f t="shared" si="40"/>
@@ -22439,7 +22453,7 @@
       </c>
       <c r="R33" s="44">
         <f t="shared" ref="R33:T33" si="47">($J33/$J$34) * (G$34/$J$34)</f>
-        <v>0.16000000000000003</v>
+        <v>0.48</v>
       </c>
       <c r="S33" s="45">
         <f t="shared" si="47"/>
@@ -22447,7 +22461,7 @@
       </c>
       <c r="T33" s="46">
         <f t="shared" si="47"/>
-        <v>0.64000000000000012</v>
+        <v>0.32000000000000006</v>
       </c>
       <c r="U33" s="11"/>
       <c r="V33" s="41" t="s">
@@ -22455,7 +22469,7 @@
       </c>
       <c r="W33" s="44">
         <f>1-W31/W32</f>
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="X33" s="46" t="s">
         <v>159</v>
@@ -22475,7 +22489,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="4">
-        <f>'Human Grading'!C34</f>
+        <f>'LLM Grading'!C34</f>
         <v>1</v>
       </c>
       <c r="E34" s="30"/>
@@ -22484,7 +22498,7 @@
       </c>
       <c r="G34" s="11">
         <f t="shared" ref="G34:I34" si="48">SUM(G31:G33)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" s="11">
         <f t="shared" si="48"/>
@@ -22492,7 +22506,7 @@
       </c>
       <c r="I34" s="11">
         <f t="shared" si="48"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J34" s="11">
         <f>SUM(G31:I33)</f>
@@ -22513,7 +22527,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4">
-        <f>'Human Grading'!C35</f>
+        <f>'LLM Grading'!C35</f>
         <v>1</v>
       </c>
       <c r="E35" s="30"/>
@@ -22532,16 +22546,16 @@
         <v>1</v>
       </c>
       <c r="D36" s="4">
-        <f>'Human Grading'!C36</f>
-        <v>1</v>
+        <f>'LLM Grading'!C36</f>
+        <v>0</v>
       </c>
       <c r="E36" s="30"/>
-      <c r="F36" s="67" t="s">
+      <c r="F36" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -22557,7 +22571,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="4">
-        <f>'Human Grading'!C37</f>
+        <f>'LLM Grading'!C37</f>
         <v>1</v>
       </c>
       <c r="E37" s="30"/>
@@ -22627,8 +22641,8 @@
         <v>1</v>
       </c>
       <c r="D38" s="4">
-        <f>'Human Grading'!C38</f>
-        <v>1</v>
+        <f>'LLM Grading'!C38</f>
+        <v>0</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="37">
@@ -22636,7 +22650,7 @@
       </c>
       <c r="G38" s="38">
         <f t="shared" ref="G38:H38" si="49">COUNTIFS($A$2:$A$90,$F$37,$C$2:$C$90,$F38,$D$2:$D$90,G$37)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="39">
         <f t="shared" si="49"/>
@@ -22644,7 +22658,7 @@
       </c>
       <c r="I38" s="40">
         <f>COUNTIFS($A$2:$A$46,$F$37,$C$2:$C$46,$F38,$D$2:$D$46,I$37)+MAX(D50-C50,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="11">
         <f t="shared" ref="J38:J40" si="50">SUM(G38:I38)</f>
@@ -22672,7 +22686,7 @@
       </c>
       <c r="R38" s="56">
         <f t="shared" ref="R38:T38" si="52">($J38/$J$41) * (G$41/$J$41)</f>
-        <v>1.2345679012345678E-2</v>
+        <v>0</v>
       </c>
       <c r="S38" s="57">
         <f t="shared" si="52"/>
@@ -22680,7 +22694,7 @@
       </c>
       <c r="T38" s="58">
         <f t="shared" si="52"/>
-        <v>9.8765432098765427E-2</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="41" t="s">
@@ -22688,7 +22702,7 @@
       </c>
       <c r="W38" s="38">
         <f>SUMPRODUCT(G38:I40, M38:O40) /$J$41</f>
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="X38" s="40" t="s">
         <v>156</v>
@@ -22708,7 +22722,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="4">
-        <f>'Human Grading'!C39</f>
+        <f>'LLM Grading'!C39</f>
         <v>1</v>
       </c>
       <c r="E39" s="30"/>
@@ -22769,7 +22783,7 @@
       </c>
       <c r="W39" s="42">
         <f>SUMPRODUCT(R38:T40, M38:O40)</f>
-        <v>0.19753086419753085</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="X39" s="43" t="s">
         <v>158</v>
@@ -22789,8 +22803,8 @@
         <v>0</v>
       </c>
       <c r="D40" s="4">
-        <f>'Human Grading'!C40</f>
-        <v>0</v>
+        <f>'LLM Grading'!C40</f>
+        <v>0.5</v>
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="37">
@@ -22834,7 +22848,7 @@
       </c>
       <c r="R40" s="61">
         <f t="shared" ref="R40:T40" si="57">($J40/$J$41) * (G$41/$J$41)</f>
-        <v>9.8765432098765427E-2</v>
+        <v>0</v>
       </c>
       <c r="S40" s="62">
         <f t="shared" si="57"/>
@@ -22842,7 +22856,7 @@
       </c>
       <c r="T40" s="63">
         <f t="shared" si="57"/>
-        <v>0.79012345679012341</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="U40" s="11"/>
       <c r="V40" s="41" t="s">
@@ -22850,7 +22864,7 @@
       </c>
       <c r="W40" s="44">
         <f>1-W38/W39</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" s="46" t="s">
         <v>159</v>
@@ -22870,7 +22884,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="4">
-        <f>'Human Grading'!C41</f>
+        <f>'LLM Grading'!C41</f>
         <v>1</v>
       </c>
       <c r="E41" s="30"/>
@@ -22879,7 +22893,7 @@
       </c>
       <c r="G41" s="11">
         <f t="shared" ref="G41:I41" si="58">SUM(G38:G40)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="11">
         <f t="shared" si="58"/>
@@ -22887,7 +22901,7 @@
       </c>
       <c r="I41" s="11">
         <f t="shared" si="58"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J41" s="11">
         <f>SUM(G38:I40)</f>
@@ -22908,7 +22922,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="4">
-        <f>'Human Grading'!C42</f>
+        <f>'LLM Grading'!C42</f>
         <v>1</v>
       </c>
       <c r="E42" s="30"/>
@@ -22927,16 +22941,16 @@
         <v>1</v>
       </c>
       <c r="D43" s="4">
-        <f>'Human Grading'!C43</f>
+        <f>'LLM Grading'!C43</f>
         <v>1</v>
       </c>
       <c r="E43" s="30"/>
-      <c r="F43" s="67" t="s">
+      <c r="F43" s="69" t="s">
         <v>150</v>
       </c>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
     </row>
     <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -22952,7 +22966,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="4">
-        <f>'Human Grading'!C44</f>
+        <f>'LLM Grading'!C44</f>
         <v>1</v>
       </c>
       <c r="E44" s="30"/>
@@ -23022,7 +23036,7 @@
         <v>0.5</v>
       </c>
       <c r="D45" s="4">
-        <f>'Human Grading'!C45</f>
+        <f>'LLM Grading'!C45</f>
         <v>0.5</v>
       </c>
       <c r="E45" s="30"/>
@@ -23103,7 +23117,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="4">
-        <f>'Human Grading'!C46</f>
+        <f>'LLM Grading'!C46</f>
         <v>1</v>
       </c>
       <c r="E46" s="30"/>
@@ -23183,9 +23197,9 @@
         <f>'Human Grading'!C47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="51">
-        <f>'Human Grading'!C47</f>
-        <v>0</v>
+      <c r="D47" s="71">
+        <f>'LLM Grading'!C47</f>
+        <v>2</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="37">
@@ -23265,7 +23279,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="4">
-        <f>'Human Grading'!C48</f>
+        <f>'LLM Grading'!C48</f>
         <v>0</v>
       </c>
       <c r="E48" s="30"/>
@@ -23303,7 +23317,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="4">
-        <f>'Human Grading'!C49</f>
+        <f>'LLM Grading'!C49</f>
         <v>0</v>
       </c>
       <c r="E49" s="30"/>
@@ -23322,16 +23336,16 @@
         <v>0</v>
       </c>
       <c r="D50" s="4">
-        <f>'Human Grading'!C50</f>
-        <v>0</v>
+        <f>'LLM Grading'!C50</f>
+        <v>1</v>
       </c>
       <c r="E50" s="30"/>
-      <c r="F50" s="67" t="s">
+      <c r="F50" s="69" t="s">
         <v>152</v>
       </c>
-      <c r="G50" s="68"/>
-      <c r="H50" s="68"/>
-      <c r="I50" s="68"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
     </row>
     <row r="51" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -23347,7 +23361,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="4">
-        <f>'Human Grading'!C51</f>
+        <f>'LLM Grading'!C51</f>
         <v>0</v>
       </c>
       <c r="E51" s="30"/>
@@ -23417,7 +23431,7 @@
         <v>0</v>
       </c>
       <c r="D52" s="4">
-        <f>'Human Grading'!C52</f>
+        <f>'LLM Grading'!C52</f>
         <v>0</v>
       </c>
       <c r="E52" s="30"/>
@@ -23462,7 +23476,7 @@
       </c>
       <c r="R52" s="38">
         <f t="shared" ref="R52:T52" si="72">($J52/$J$55) * (G$55/$J$55)</f>
-        <v>0.44444444444444442</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="S52" s="39">
         <f t="shared" si="72"/>
@@ -23470,7 +23484,7 @@
       </c>
       <c r="T52" s="40">
         <f t="shared" si="72"/>
-        <v>0.22222222222222221</v>
+        <v>0</v>
       </c>
       <c r="U52" s="11"/>
       <c r="V52" s="41" t="s">
@@ -23478,7 +23492,7 @@
       </c>
       <c r="W52" s="38">
         <f>SUMPRODUCT(G52:I54, M52:O54) /$J$55</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="X52" s="40" t="s">
         <v>156</v>
@@ -23498,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="4">
-        <f>'Human Grading'!C53</f>
+        <f>'LLM Grading'!C53</f>
         <v>0</v>
       </c>
       <c r="E53" s="30"/>
@@ -23559,7 +23573,7 @@
       </c>
       <c r="W53" s="42">
         <f>SUMPRODUCT(R52:T54, M52:O54)</f>
-        <v>0.44444444444444442</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="X53" s="43" t="s">
         <v>158</v>
@@ -23576,7 +23590,7 @@
       </c>
       <c r="G54" s="44">
         <f>COUNTIFS($A$2:$A$46,$F$51,$C$2:$C$46,$F54,$D$2:$D$46,G$51) + MAX(C52-D52,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="45">
         <f>COUNTIFS($A$2:$A$90,$F$51,$C$2:$C$90,$F54,$D$2:$D$90,H$51)</f>
@@ -23584,7 +23598,7 @@
       </c>
       <c r="I54" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$51,$C$2:$C$46,$F54,$D$2:$D$46,I$51)+MIN(C52,D52)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="11">
         <f t="shared" si="70"/>
@@ -23612,7 +23626,7 @@
       </c>
       <c r="R54" s="44">
         <f t="shared" ref="R54:T54" si="77">($J54/$J$55) * (G$55/$J$55)</f>
-        <v>0.22222222222222221</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="S54" s="45">
         <f t="shared" si="77"/>
@@ -23620,7 +23634,7 @@
       </c>
       <c r="T54" s="46">
         <f t="shared" si="77"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="41" t="s">
@@ -23628,7 +23642,7 @@
       </c>
       <c r="W54" s="44">
         <f>1-W52/W53</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54" s="46" t="s">
         <v>159</v>
@@ -23645,7 +23659,7 @@
       </c>
       <c r="G55" s="11">
         <f t="shared" ref="G55:I55" si="78">SUM(G52:G54)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="11">
         <f t="shared" si="78"/>
@@ -23653,7 +23667,7 @@
       </c>
       <c r="I55" s="11">
         <f t="shared" si="78"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="11">
         <f>SUM(G52:I54)</f>
